--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75063</v>
+        <v>16.76667</v>
       </c>
       <c r="D2" t="n">
-        <v>16.37317</v>
+        <v>16.63754</v>
       </c>
       <c r="E2" t="n">
-        <v>16.52495</v>
+        <v>16.71482</v>
       </c>
       <c r="F2" t="n">
-        <v>43.09026</v>
+        <v>41.58349</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04968</v>
+        <v>0.05076</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81162</v>
+        <v>1.82223</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8214</v>
+        <v>16.87409</v>
       </c>
       <c r="D3" t="n">
-        <v>16.23541</v>
+        <v>16.27136</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72434</v>
+        <v>16.83921</v>
       </c>
       <c r="F3" t="n">
-        <v>41.94209</v>
+        <v>42.04211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05036</v>
+        <v>0.05042</v>
       </c>
       <c r="H3" t="n">
-        <v>1.76123</v>
+        <v>1.76695</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72814</v>
+        <v>16.64248</v>
       </c>
       <c r="D4" t="n">
-        <v>16.47683</v>
+        <v>16.50482</v>
       </c>
       <c r="E4" t="n">
-        <v>16.92294</v>
+        <v>16.58352</v>
       </c>
       <c r="F4" t="n">
-        <v>41.88605</v>
+        <v>41.44639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04998</v>
+        <v>0.05088</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80698</v>
+        <v>1.82356</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.60948</v>
+        <v>16.41863</v>
       </c>
       <c r="D6" t="n">
-        <v>15.81139</v>
+        <v>16.05517</v>
       </c>
       <c r="E6" t="n">
-        <v>16.32105</v>
+        <v>16.35133</v>
       </c>
       <c r="F6" t="n">
-        <v>21.2717</v>
+        <v>21.98389</v>
       </c>
       <c r="G6" t="n">
-        <v>33.70798</v>
+        <v>33.13912</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.82177</v>
+        <v>16.73095</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03412</v>
+        <v>15.92209</v>
       </c>
       <c r="E7" t="n">
-        <v>16.26903</v>
+        <v>16.35394</v>
       </c>
       <c r="F7" t="n">
-        <v>21.48879</v>
+        <v>21.96003</v>
       </c>
       <c r="G7" t="n">
-        <v>34.04165</v>
+        <v>33.78807</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.94284</v>
+        <v>16.60614</v>
       </c>
       <c r="D8" t="n">
-        <v>15.98764</v>
+        <v>16.19474</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46771</v>
+        <v>16.48134</v>
       </c>
       <c r="F8" t="n">
-        <v>21.67595</v>
+        <v>21.92918</v>
       </c>
       <c r="G8" t="n">
-        <v>33.95043</v>
+        <v>33.50981</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60639</v>
+        <v>0.59975</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10219</v>
+        <v>1.10385</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6160099999999999</v>
+        <v>0.6085199999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10848</v>
+        <v>1.11582</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5976900000000001</v>
+        <v>0.59911</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10922</v>
+        <v>1.11545</v>
       </c>
     </row>
   </sheetData>
